--- a/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,110 +484,130 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Diesel_Compressor_PRatio_abs</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Diesel_Compressor_VolFlow_m3_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Diesel_P_i_MF_mbar</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Diesel_Eta_v_pct</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Diesel_Q_intercooler_kW</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Diesel_n_th_pct</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>E94H6_Speed_RPM</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>E94H6_Power_kW</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_L_h</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_kWh</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>E94H6_Torque_Nm</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>E94H6_BMEP_bar</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h_kW</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>E94H6_Compressor_PRatio_abs</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>E94H6_Compressor_VolFlow_m3_s</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>E94H6_P_i_MF_mbar</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>E94H6_Eta_v_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>E94H6_Q_intercooler_kW</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>E94H6_n_th_pct</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
@@ -637,70 +657,78 @@
       <c r="M2" t="n">
         <v>3.862228663873061</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>1383.7706061</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>199.4328866534262</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>25.99995209197379</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>43.21582376606398</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>899.965</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>153.0359</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>59.591</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>73.66007416563659</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>154.6861557478368</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>1.010783455044449</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>1633.001</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>15.90767114699158</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>493.8484</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>3.227010132916525</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
+        <v>1.665849595546522</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1214716774344878</v>
+      </c>
+      <c r="AF2" t="n">
         <v>626.0135</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
         <v>125.9094696987295</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
         <v>6.396908493687032</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AI2" t="n">
         <v>37.58201332579686</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AJ2" t="n">
         <v>-113.8359507901702</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AK2" t="n">
         <v>-42.39351175135284</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AL2" t="n">
         <v>-0.256900819510987</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AM2" t="n">
         <v>-20.2653629667434</v>
       </c>
     </row>
@@ -748,70 +776,78 @@
       <c r="M3" t="n">
         <v>4.136611124591413</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>1808.42287132</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>237.7665274826089</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>39.21109490130724</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>44.48653525713356</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>999.899</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>182.1889</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>70.161</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>86.72558714462299</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>182.1237330037083</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.9996423108307273</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>1744.402</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>16.9928697925809</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>577.2861</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>3.168612906713856</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
+        <v>1.756373160341248</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1432382602577588</v>
+      </c>
+      <c r="AF3" t="n">
         <v>696.9444</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
         <v>132.4059801264863</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>8.514083455979099</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>38.00086977651749</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AJ3" t="n">
         <v>-135.379352970688</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AK3" t="n">
         <v>-42.63875185818039</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AL3" t="n">
         <v>-0.2318318843059595</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AM3" t="n">
         <v>-18.82555763015622</v>
       </c>
     </row>
@@ -859,70 +895,78 @@
       <c r="M4" t="n">
         <v>4.439412673420192</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>2068.45330718</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>260.4278275653932</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>49.21946241193401</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>44.80652170493985</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1100.059</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>236.6207</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>90.709</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>112.1248454882571</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>235.4621755253399</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.9951038752118473</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>2059.023</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>20.05771017169742</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>732.7568</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>3.096756961669034</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
+        <v>2.083584172827948</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1858725235512771</v>
+      </c>
+      <c r="AF4" t="n">
         <v>966.657</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
         <v>152.8105691663256</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>15.23641710058327</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
         <v>38.17418283984513</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AJ4" t="n">
         <v>-113.849790921741</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AK4" t="n">
         <v>-32.5925825215005</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AL4" t="n">
         <v>-0.2275757284619757</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AM4" t="n">
         <v>-18.61286699951254</v>
       </c>
     </row>
@@ -970,70 +1014,78 @@
       <c r="M5" t="n">
         <v>4.351854783728491</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>2103.78106115</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>264.1959399479355</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>53.55340502049638</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>44.54043869545165</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>1199.668</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>261.7221</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>99.86499999999999</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>123.442521631644</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>259.2292954264524</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.9904753760819295</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2087.014</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>20.33038093128387</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>802.8339999999999</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>3.067505571749577</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
+        <v>2.15411729161031</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2062992930795192</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1003.726</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AG5" t="n">
         <v>153.3635080573405</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AH5" t="n">
         <v>17.74821902428575</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AI5" t="n">
         <v>38.35257109292667</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
         <v>-134.8767043913437</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AK5" t="n">
         <v>-34.22345877852664</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AL5" t="n">
         <v>-0.2395084724110762</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AM5" t="n">
         <v>-19.47248922858016</v>
       </c>
     </row>
@@ -1081,70 +1133,78 @@
       <c r="M6" t="n">
         <v>4.337543110523877</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>2108.71964232</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>263.636130795378</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>57.08083544388736</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>44.29541275227747</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1300.024</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>280.1731</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>107.281</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>132.6093943139679</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>278.4797280593326</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.9939559795688186</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>2062.997</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>20.0964223862877</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>859.04</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>3.066104490402541</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
+        <v>2.180324876051744</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2229211108269001</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1003.352</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AG6" t="n">
         <v>151.3299523887224</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AH6" t="n">
         <v>19.44642153696666</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AI6" t="n">
         <v>38.21826927733208</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AJ6" t="n">
         <v>-149.5429293920391</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AK6" t="n">
         <v>-34.9380872224104</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AL6" t="n">
         <v>-0.2428316875103567</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AM6" t="n">
         <v>-19.63406443757911</v>
       </c>
     </row>
@@ -1192,70 +1252,78 @@
       <c r="M7" t="n">
         <v>4.332122930443129</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>2087.90902829</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>261.1287621659193</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>59.57143091889137</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>43.92148191895775</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1400.075</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>300.4143</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>115.281</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>142.4981458590853</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>299.2461063040791</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.9961113911823742</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2052.946</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>19.99851185059396</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>924.624</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>3.07782951743642</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
+        <v>2.241967495027866</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2429402815528524</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1029.969</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AG7" t="n">
         <v>151.4528223795006</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
         <v>21.8214326817</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AI7" t="n">
         <v>38.1355715969526</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
         <v>-159.0279808018529</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AK7" t="n">
         <v>-34.70149966500132</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AL7" t="n">
         <v>-0.251205816859098</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AM7" t="n">
         <v>-20.13968982706007</v>
       </c>
     </row>
@@ -1303,70 +1371,78 @@
       <c r="M8" t="n">
         <v>4.347692441495634</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>2090.40048932</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>260.6430087969362</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>63.15925558260871</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>43.32666532362657</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1500.016</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>301.1655</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>116.68</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>144.2274412855377</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>302.8776266996292</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>1.00568500276303</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>1920.083</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>18.70424386692295</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>933.568</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>3.099850414473105</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
+        <v>2.15791880391235</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2457504738434706</v>
+      </c>
+      <c r="AF8" t="n">
         <v>945.126</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AG8" t="n">
         <v>142.6978264604757</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AH8" t="n">
         <v>20.80657339648533</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
         <v>37.77254028111073</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AJ8" t="n">
         <v>-188.6036641584247</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AK8" t="n">
         <v>-38.37453585041873</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AL8" t="n">
         <v>-0.2587561858443008</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AM8" t="n">
         <v>-20.46407442083548</v>
       </c>
     </row>
@@ -1414,70 +1490,78 @@
       <c r="M9" t="n">
         <v>4.456480230588814</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>2003.24394734</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>254.307230603555</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>65.04774618537127</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>42.7827691460166</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1600.038</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>300.3554</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>117.308</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>145.0037082818294</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>304.5077873918418</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>1.013824913392074</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>1795.378</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>17.48944600067205</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>939.66</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>3.12849377770468</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
+        <v>2.08444373829525</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2476852341967574</v>
+      </c>
+      <c r="AF9" t="n">
         <v>871.4739999999999</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AG9" t="n">
         <v>134.7685023601441</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
         <v>19.76882940174999</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
         <v>37.46926789348365</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AJ9" t="n">
         <v>-200.4422911503153</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AK9" t="n">
         <v>-39.69546687249021</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AL9" t="n">
         <v>-0.2666910815689301</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AM9" t="n">
         <v>-20.8268450076683</v>
       </c>
     </row>
@@ -1525,70 +1609,78 @@
       <c r="M10" t="n">
         <v>4.53941845037895</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>1872.93741169</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>241.8846982364728</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>64.1654884816061</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>42.52423108019509</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>1699.999</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>296.0968</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>117.119</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>144.770086526576</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>304.0171817058097</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>1.026749298559828</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>1665.875</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>16.22790902883379</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>935.774</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>3.16036512383788</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
+        <v>1.998451808424485</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.2463620050651257</v>
+      </c>
+      <c r="AF10" t="n">
         <v>791.2596</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AG10" t="n">
         <v>126.3173259000818</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AH10" t="n">
         <v>18.32208567917583</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
         <v>36.99761697452185</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AJ10" t="n">
         <v>-201.5752495973791</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AK10" t="n">
         <v>-39.86911929789162</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AL10" t="n">
         <v>-0.2615519548333953</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AM10" t="n">
         <v>-20.30208028941215</v>
       </c>
     </row>
@@ -1636,70 +1728,78 @@
       <c r="M11" t="n">
         <v>4.661451409354044</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>1824.85529229</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>236.7196328849409</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>66.41701487097963</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>41.97438206424157</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>1799.979</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>291.8231</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>116.542</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>144.0568603213844</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>302.5194066749073</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>1.036653392671476</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1551.491</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>15.11365186887033</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>931.751</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>3.192862388207102</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
+        <v>1.925254237226219</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.2448460278463756</v>
+      </c>
+      <c r="AF11" t="n">
         <v>722.6549</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AG11" t="n">
         <v>118.9052406400124</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AH11" t="n">
         <v>16.99069460301212</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AI11" t="n">
         <v>36.64414503972399</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AJ11" t="n">
         <v>-212.5273480354093</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AK11" t="n">
         <v>-41.26370006057864</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AL11" t="n">
         <v>-0.2685241348106859</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AM11" t="n">
         <v>-20.57376327408119</v>
       </c>
     </row>

--- a/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -657,8 +657,12 @@
       <c r="M2" t="n">
         <v>3.862228663873061</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2.394947865647763</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1906927639437788</v>
+      </c>
       <c r="P2" t="n">
         <v>1383.7706061</v>
       </c>
@@ -776,8 +780,12 @@
       <c r="M3" t="n">
         <v>4.136611124591413</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2.847439177810685</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2506917189847213</v>
+      </c>
       <c r="P3" t="n">
         <v>1808.42287132</v>
       </c>
@@ -895,8 +903,12 @@
       <c r="M4" t="n">
         <v>4.439412673420192</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>3.139663848283791</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3006765122493675</v>
+      </c>
       <c r="P4" t="n">
         <v>2068.45330718</v>
       </c>
@@ -1014,8 +1026,12 @@
       <c r="M5" t="n">
         <v>4.351854783728491</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>3.201759989156442</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3326502254066982</v>
+      </c>
       <c r="P5" t="n">
         <v>2103.78106115</v>
       </c>
@@ -1133,8 +1149,12 @@
       <c r="M6" t="n">
         <v>4.337543110523877</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>3.236706916900525</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3601964987750724</v>
+      </c>
       <c r="P6" t="n">
         <v>2108.71964232</v>
       </c>
@@ -1252,8 +1272,12 @@
       <c r="M7" t="n">
         <v>4.332122930443129</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>3.241943089107858</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3841165943639843</v>
+      </c>
       <c r="P7" t="n">
         <v>2087.90902829</v>
       </c>
@@ -1371,8 +1395,12 @@
       <c r="M8" t="n">
         <v>4.347692441495634</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>3.278674470393804</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4104028682278533</v>
+      </c>
       <c r="P8" t="n">
         <v>2090.40048932</v>
       </c>
@@ -1490,8 +1518,12 @@
       <c r="M9" t="n">
         <v>4.456480230588814</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>3.209033350920502</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4285883475937811</v>
+      </c>
       <c r="P9" t="n">
         <v>2003.24394734</v>
       </c>
@@ -1609,8 +1641,12 @@
       <c r="M10" t="n">
         <v>4.53941845037895</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>3.083141085728647</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4353538353188192</v>
+      </c>
       <c r="P10" t="n">
         <v>1872.93741169</v>
       </c>
@@ -1728,8 +1764,12 @@
       <c r="M11" t="n">
         <v>4.661451409354044</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>3.052200566203288</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4512066176176181</v>
+      </c>
       <c r="P11" t="n">
         <v>1824.85529229</v>
       </c>

--- a/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,110 +504,120 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Diesel_Eta_v_corr_press_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>Diesel_Q_intercooler_kW</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Diesel_n_th_pct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>E94H6_Speed_RPM</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>E94H6_Power_kW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_L_h</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_kWh</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>E94H6_Torque_Nm</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>E94H6_BMEP_bar</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h_kW</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>E94H6_Compressor_PRatio_abs</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>E94H6_Compressor_VolFlow_m3_s</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>E94H6_P_i_MF_mbar</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>E94H6_Eta_v_pct</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>E94H6_Eta_v_corr_press_pct</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>E94H6_Q_intercooler_kW</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>E94H6_n_th_pct</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
@@ -670,69 +680,75 @@
         <v>199.4328866534262</v>
       </c>
       <c r="R2" t="n">
+        <v>84.29071754541188</v>
+      </c>
+      <c r="S2" t="n">
         <v>25.99995209197379</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>43.21582376606398</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>899.965</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>153.0359</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>59.591</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>73.66007416563659</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>154.6861557478368</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>1.010783455044449</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>1633.001</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>15.90767114699158</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>493.8484</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>3.227010132916525</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>1.665849595546522</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.1214716774344878</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>626.0135</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>125.9094696987295</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
+        <v>77.81893974931444</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>6.396908493687032</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AK2" t="n">
         <v>37.58201332579686</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>-113.8359507901702</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>-42.39351175135284</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>-0.256900819510987</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AO2" t="n">
         <v>-20.2653629667434</v>
       </c>
     </row>
@@ -793,69 +809,75 @@
         <v>237.7665274826089</v>
       </c>
       <c r="R3" t="n">
+        <v>85.36738494190979</v>
+      </c>
+      <c r="S3" t="n">
         <v>39.21109490130724</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>44.48653525713356</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>999.899</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>182.1889</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>70.161</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>86.72558714462299</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>182.1237330037083</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>0.9996423108307273</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>1744.402</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>16.9928697925809</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>577.2861</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>3.168612906713856</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>1.756373160341248</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.1432382602577588</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>696.9444</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>132.4059801264863</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>78.43954333727494</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>8.514083455979099</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>38.00086977651749</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>-135.379352970688</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>-42.63875185818039</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>-0.2318318843059595</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AO3" t="n">
         <v>-18.82555763015622</v>
       </c>
     </row>
@@ -916,69 +938,75 @@
         <v>260.4278275653932</v>
       </c>
       <c r="R4" t="n">
+        <v>85.61330094116298</v>
+      </c>
+      <c r="S4" t="n">
         <v>49.21946241193401</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>44.80652170493985</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1100.059</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>236.6207</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>90.709</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>112.1248454882571</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>235.4621755253399</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>0.9951038752118473</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>2059.023</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>20.05771017169742</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>732.7568</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>3.096756961669034</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2.083584172827948</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>0.1858725235512771</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>966.657</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>152.8105691663256</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
+        <v>78.19390256266</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>15.23641710058327</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>38.17418283984513</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>-113.849790921741</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>-32.5925825215005</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>-0.2275757284619757</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
         <v>-18.61286699951254</v>
       </c>
     </row>
@@ -1039,69 +1067,75 @@
         <v>264.1959399479355</v>
       </c>
       <c r="R5" t="n">
+        <v>85.86759285187357</v>
+      </c>
+      <c r="S5" t="n">
         <v>53.55340502049638</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>44.54043869545165</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1199.668</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>261.7221</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>99.86499999999999</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>123.442521631644</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>259.2292954264524</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0.9904753760819295</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>2087.014</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>20.33038093128387</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>802.8339999999999</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>3.067505571749577</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>2.15411729161031</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>0.2062992930795192</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>1003.726</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>153.3635080573405</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
+        <v>77.03437832511007</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>17.74821902428575</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>38.35257109292667</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AL5" t="n">
         <v>-134.8767043913437</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>-34.22345877852664</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>-0.2395084724110762</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
         <v>-19.47248922858016</v>
       </c>
     </row>
@@ -1162,69 +1196,75 @@
         <v>263.636130795378</v>
       </c>
       <c r="R6" t="n">
+        <v>85.550091326344</v>
+      </c>
+      <c r="S6" t="n">
         <v>57.08083544388736</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>44.29541275227747</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1300.024</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>280.1731</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>107.281</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>132.6093943139679</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>278.4797280593326</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>0.9939559795688186</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>2062.997</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>20.0964223862877</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>859.04</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>3.066104490402541</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>2.180324876051744</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>0.2229211108269001</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>1003.352</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>151.3299523887224</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
+        <v>76.02702393717755</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>19.44642153696666</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>38.21826927733208</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AL6" t="n">
         <v>-149.5429293920391</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>-34.9380872224104</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>-0.2428316875103567</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
         <v>-19.63406443757911</v>
       </c>
     </row>
@@ -1285,69 +1325,75 @@
         <v>261.1287621659193</v>
       </c>
       <c r="R7" t="n">
+        <v>85.30512622614667</v>
+      </c>
+      <c r="S7" t="n">
         <v>59.57143091889137</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>43.92148191895775</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1400.075</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>300.4143</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>115.281</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>142.4981458590853</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>299.2461063040791</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0.9961113911823742</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>2052.946</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>19.99851185059396</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>924.624</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>3.07782951743642</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>2.241967495027866</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>0.2429402815528524</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1029.969</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>151.4528223795006</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
+        <v>75.09742393077627</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>21.8214326817</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>38.1355715969526</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AL7" t="n">
         <v>-159.0279808018529</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>-34.70149966500132</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>-0.251205816859098</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
         <v>-20.13968982706007</v>
       </c>
     </row>
@@ -1408,69 +1454,75 @@
         <v>260.6430087969362</v>
       </c>
       <c r="R8" t="n">
+        <v>85.07808412737261</v>
+      </c>
+      <c r="S8" t="n">
         <v>63.15925558260871</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>43.32666532362657</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1500.016</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>301.1655</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>116.68</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>144.2274412855377</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>302.8776266996292</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.00568500276303</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>1920.083</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>18.70424386692295</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>933.568</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>3.099850414473105</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>2.15791880391235</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>0.2457504738434706</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>945.126</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>142.6978264604757</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
+        <v>73.8220616060774</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>20.80657339648533</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>37.77254028111073</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AL8" t="n">
         <v>-188.6036641584247</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>-38.37453585041873</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>-0.2587561858443008</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>-20.46407442083548</v>
       </c>
     </row>
@@ -1531,69 +1583,75 @@
         <v>254.307230603555</v>
       </c>
       <c r="R9" t="n">
+        <v>85.40861717388215</v>
+      </c>
+      <c r="S9" t="n">
         <v>65.04774618537127</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>42.7827691460166</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1600.038</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>300.3554</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>117.308</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>145.0037082818294</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>304.5077873918418</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>1.013824913392074</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>1795.378</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>17.48944600067205</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>939.66</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>3.12849377770468</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>2.08444373829525</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>0.2476852341967574</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>871.4739999999999</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>134.7685023601441</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
+        <v>72.44488005184792</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>19.76882940174999</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>37.46926789348365</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
         <v>-200.4422911503153</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>-39.69546687249021</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>-0.2666910815689301</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
         <v>-20.8268450076683</v>
       </c>
     </row>
@@ -1654,69 +1712,75 @@
         <v>241.8846982364728</v>
       </c>
       <c r="R10" t="n">
+        <v>84.90454377874335</v>
+      </c>
+      <c r="S10" t="n">
         <v>64.1654884816061</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>42.52423108019509</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1699.999</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>296.0968</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>117.119</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>144.770086526576</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>304.0171817058097</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.026749298559828</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>1665.875</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>16.22790902883379</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>935.774</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>3.16036512383788</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>1.998451808424485</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>0.2463620050651257</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>791.2596</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>126.3173259000818</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>70.92075394072056</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>18.32208567917583</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>36.99761697452185</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
         <v>-201.5752495973791</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AM10" t="n">
         <v>-39.86911929789162</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
         <v>-0.2615519548333953</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
         <v>-20.30208028941215</v>
       </c>
     </row>
@@ -1777,69 +1841,75 @@
         <v>236.7196328849409</v>
       </c>
       <c r="R11" t="n">
+        <v>84.49937132592183</v>
+      </c>
+      <c r="S11" t="n">
         <v>66.41701487097963</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>41.97438206424157</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1799.979</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>291.8231</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>116.542</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>144.0568603213844</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>302.5194066749073</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>1.036653392671476</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>1551.491</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>15.11365186887033</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>931.751</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>3.192862388207102</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>1.925254237226219</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>0.2448460278463756</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>722.6549</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>118.9052406400124</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
+        <v>69.39801729498907</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>16.99069460301212</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>36.64414503972399</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AL11" t="n">
         <v>-212.5273480354093</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AM11" t="n">
         <v>-41.26370006057864</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>-0.2685241348106859</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
         <v>-20.57376327408119</v>
       </c>
     </row>

--- a/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,6 +622,61 @@
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>E94H6_PCYL1</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>E94H6_APMAX1</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>E94H6_PMAX1</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>E94H6_IMEP1</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>E94H6_IMEPH1</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>E94H6_IMPEL1</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>E94H6_AI05_1</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>E94H6_AI10_1</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>E94H6_AI50_1</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>E94H6_AI90_1</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>E94H6_RMAX1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,121 +690,154 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>899.807285636</v>
+        <v>999.657661495</v>
       </c>
       <c r="E2" t="n">
-        <v>211.820965147</v>
+        <v>257.823580249</v>
       </c>
       <c r="F2" t="n">
-        <v>42.4165475698</v>
+        <v>50.1537282104</v>
       </c>
       <c r="G2" t="n">
-        <v>49.72631602555686</v>
+        <v>58.79686777303634</v>
       </c>
       <c r="H2" t="n">
-        <v>268.5221065380071</v>
+        <v>317.5030859743962</v>
       </c>
       <c r="I2" t="n">
-        <v>1.267684274555436</v>
+        <v>1.231474195136687</v>
       </c>
       <c r="J2" t="n">
-        <v>2247.96135288</v>
+        <v>2462.87816125</v>
       </c>
       <c r="K2" t="n">
-        <v>21.89822905972583</v>
+        <v>23.99181376145656</v>
       </c>
       <c r="L2" t="n">
-        <v>818.1010032</v>
+        <v>1066.51589024</v>
       </c>
       <c r="M2" t="n">
-        <v>3.862228663873061</v>
+        <v>4.136611124591413</v>
       </c>
       <c r="N2" t="n">
-        <v>2.394947865647763</v>
+        <v>2.847439177810685</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1906927639437788</v>
+        <v>0.2506917189847213</v>
       </c>
       <c r="P2" t="n">
-        <v>1383.7706061</v>
+        <v>1808.42287132</v>
       </c>
       <c r="Q2" t="n">
-        <v>199.4328866534262</v>
+        <v>237.7665274826089</v>
       </c>
       <c r="R2" t="n">
-        <v>84.29071754541188</v>
+        <v>85.36738494190979</v>
       </c>
       <c r="S2" t="n">
-        <v>25.99995209197379</v>
+        <v>39.21109490130724</v>
       </c>
       <c r="T2" t="n">
-        <v>43.21582376606398</v>
+        <v>44.48653525713356</v>
       </c>
       <c r="U2" t="n">
-        <v>899.965</v>
+        <v>999.899</v>
       </c>
       <c r="V2" t="n">
-        <v>153.0359</v>
+        <v>182.1889</v>
       </c>
       <c r="W2" t="n">
-        <v>59.591</v>
+        <v>70.161</v>
       </c>
       <c r="X2" t="n">
-        <v>73.66007416563659</v>
+        <v>86.72558714462299</v>
       </c>
       <c r="Y2" t="n">
-        <v>154.6861557478368</v>
+        <v>182.1237330037083</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.010783455044449</v>
+        <v>0.9996423108307273</v>
       </c>
       <c r="AA2" t="n">
-        <v>1633.001</v>
+        <v>1744.402</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.90767114699158</v>
+        <v>16.9928697925809</v>
       </c>
       <c r="AC2" t="n">
-        <v>493.8484</v>
+        <v>577.2861</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.227010132916525</v>
+        <v>3.168612906713856</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.665849595546522</v>
+        <v>1.756373160341248</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1214716774344878</v>
+        <v>0.1432382602577588</v>
       </c>
       <c r="AG2" t="n">
-        <v>626.0135</v>
+        <v>696.9444</v>
       </c>
       <c r="AH2" t="n">
-        <v>125.9094696987295</v>
+        <v>132.4059801264863</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.81893974931444</v>
+        <v>78.43954333727494</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.396908493687032</v>
+        <v>8.514083455979099</v>
       </c>
       <c r="AK2" t="n">
-        <v>37.58201332579686</v>
+        <v>38.00086977651749</v>
       </c>
       <c r="AL2" t="n">
-        <v>-113.8359507901702</v>
+        <v>-135.379352970688</v>
       </c>
       <c r="AM2" t="n">
-        <v>-42.39351175135284</v>
+        <v>-42.63875185818039</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.256900819510987</v>
+        <v>-0.2318318843059595</v>
       </c>
       <c r="AO2" t="n">
-        <v>-20.2653629667434</v>
+        <v>-18.82555763015622</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.842295</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18.83871</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>82.21657999999999</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>17.30689</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17.0735</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.2306909</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.830645</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.524194</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14.81452</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.752198</v>
       </c>
     </row>
     <row r="3">
@@ -764,121 +852,154 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D3" t="n">
-        <v>999.657661495</v>
+        <v>1099.76545523</v>
       </c>
       <c r="E3" t="n">
-        <v>257.823580249</v>
+        <v>285.693787152</v>
       </c>
       <c r="F3" t="n">
-        <v>50.1537282104</v>
+        <v>55.1783532184</v>
       </c>
       <c r="G3" t="n">
-        <v>58.79686777303634</v>
+        <v>64.68740119390387</v>
       </c>
       <c r="H3" t="n">
-        <v>317.5030859743962</v>
+        <v>349.3119664470809</v>
       </c>
       <c r="I3" t="n">
-        <v>1.231474195136687</v>
+        <v>1.222679603673823</v>
       </c>
       <c r="J3" t="n">
-        <v>2462.87816125</v>
+        <v>2480.66514028</v>
       </c>
       <c r="K3" t="n">
-        <v>23.99181376145656</v>
+        <v>24.16508335106959</v>
       </c>
       <c r="L3" t="n">
-        <v>1066.51589024</v>
+        <v>1268.3126194</v>
       </c>
       <c r="M3" t="n">
-        <v>4.136611124591413</v>
+        <v>4.439412673420192</v>
       </c>
       <c r="N3" t="n">
-        <v>2.847439177810685</v>
+        <v>3.139663848283791</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2506917189847213</v>
+        <v>0.3006765122493675</v>
       </c>
       <c r="P3" t="n">
-        <v>1808.42287132</v>
+        <v>2068.45330718</v>
       </c>
       <c r="Q3" t="n">
-        <v>237.7665274826089</v>
+        <v>260.4278275653932</v>
       </c>
       <c r="R3" t="n">
-        <v>85.36738494190979</v>
+        <v>85.61330094116298</v>
       </c>
       <c r="S3" t="n">
-        <v>39.21109490130724</v>
+        <v>49.21946241193401</v>
       </c>
       <c r="T3" t="n">
-        <v>44.48653525713356</v>
+        <v>44.80652170493985</v>
       </c>
       <c r="U3" t="n">
-        <v>999.899</v>
+        <v>1100.059</v>
       </c>
       <c r="V3" t="n">
-        <v>182.1889</v>
+        <v>236.6207</v>
       </c>
       <c r="W3" t="n">
-        <v>70.161</v>
+        <v>90.709</v>
       </c>
       <c r="X3" t="n">
-        <v>86.72558714462299</v>
+        <v>112.1248454882571</v>
       </c>
       <c r="Y3" t="n">
-        <v>182.1237330037083</v>
+        <v>235.4621755253399</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9996423108307273</v>
+        <v>0.9951038752118473</v>
       </c>
       <c r="AA3" t="n">
-        <v>1744.402</v>
+        <v>2059.023</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.9928697925809</v>
+        <v>20.05771017169742</v>
       </c>
       <c r="AC3" t="n">
-        <v>577.2861</v>
+        <v>732.7568</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.168612906713856</v>
+        <v>3.096756961669034</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.756373160341248</v>
+        <v>2.083584172827948</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1432382602577588</v>
+        <v>0.1858725235512771</v>
       </c>
       <c r="AG3" t="n">
-        <v>696.9444</v>
+        <v>966.657</v>
       </c>
       <c r="AH3" t="n">
-        <v>132.4059801264863</v>
+        <v>152.8105691663256</v>
       </c>
       <c r="AI3" t="n">
-        <v>78.43954333727494</v>
+        <v>78.19390256266</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.514083455979099</v>
+        <v>15.23641710058327</v>
       </c>
       <c r="AK3" t="n">
-        <v>38.00086977651749</v>
+        <v>38.17418283984513</v>
       </c>
       <c r="AL3" t="n">
-        <v>-135.379352970688</v>
+        <v>-113.849790921741</v>
       </c>
       <c r="AM3" t="n">
-        <v>-42.63875185818039</v>
+        <v>-32.5925825215005</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.2318318843059595</v>
+        <v>-0.2275757284619757</v>
       </c>
       <c r="AO3" t="n">
-        <v>-18.82555763015622</v>
+        <v>-18.61286699951254</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.045549</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>20.0625</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>91.62649999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>20.11664</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19.89136</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.2224995</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.226563</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8.109375</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16.04688</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>29.47656</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.63861</v>
       </c>
     </row>
     <row r="4">
@@ -893,121 +1014,154 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D4" t="n">
-        <v>1099.76545523</v>
+        <v>1199.86290992</v>
       </c>
       <c r="E4" t="n">
-        <v>285.693787152</v>
+        <v>320.415589441</v>
       </c>
       <c r="F4" t="n">
-        <v>55.1783532184</v>
+        <v>62.2541514527</v>
       </c>
       <c r="G4" t="n">
-        <v>64.68740119390387</v>
+        <v>72.98259255885112</v>
       </c>
       <c r="H4" t="n">
-        <v>349.3119664470809</v>
+        <v>394.1059998177961</v>
       </c>
       <c r="I4" t="n">
-        <v>1.222679603673823</v>
+        <v>1.229983848493006</v>
       </c>
       <c r="J4" t="n">
-        <v>2480.66514028</v>
+        <v>2550.09139118</v>
       </c>
       <c r="K4" t="n">
-        <v>24.16508335106959</v>
+        <v>24.84139032717415</v>
       </c>
       <c r="L4" t="n">
-        <v>1268.3126194</v>
+        <v>1394.40211569</v>
       </c>
       <c r="M4" t="n">
-        <v>4.439412673420192</v>
+        <v>4.351854783728491</v>
       </c>
       <c r="N4" t="n">
-        <v>3.139663848283791</v>
+        <v>3.201759989156442</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3006765122493675</v>
+        <v>0.3326502254066982</v>
       </c>
       <c r="P4" t="n">
-        <v>2068.45330718</v>
+        <v>2103.78106115</v>
       </c>
       <c r="Q4" t="n">
-        <v>260.4278275653932</v>
+        <v>264.1959399479355</v>
       </c>
       <c r="R4" t="n">
-        <v>85.61330094116298</v>
+        <v>85.86759285187357</v>
       </c>
       <c r="S4" t="n">
-        <v>49.21946241193401</v>
+        <v>53.55340502049638</v>
       </c>
       <c r="T4" t="n">
-        <v>44.80652170493985</v>
+        <v>44.54043869545165</v>
       </c>
       <c r="U4" t="n">
-        <v>1100.059</v>
+        <v>1199.668</v>
       </c>
       <c r="V4" t="n">
-        <v>236.6207</v>
+        <v>261.7221</v>
       </c>
       <c r="W4" t="n">
-        <v>90.709</v>
+        <v>99.86499999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>112.1248454882571</v>
+        <v>123.442521631644</v>
       </c>
       <c r="Y4" t="n">
-        <v>235.4621755253399</v>
+        <v>259.2292954264524</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9951038752118473</v>
+        <v>0.9904753760819295</v>
       </c>
       <c r="AA4" t="n">
-        <v>2059.023</v>
+        <v>2087.014</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.05771017169742</v>
+        <v>20.33038093128387</v>
       </c>
       <c r="AC4" t="n">
-        <v>732.7568</v>
+        <v>802.8339999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.096756961669034</v>
+        <v>3.067505571749577</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.083584172827948</v>
+        <v>2.15411729161031</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1858725235512771</v>
+        <v>0.2062992930795192</v>
       </c>
       <c r="AG4" t="n">
-        <v>966.657</v>
+        <v>1003.726</v>
       </c>
       <c r="AH4" t="n">
-        <v>152.8105691663256</v>
+        <v>153.3635080573405</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.19390256266</v>
+        <v>77.03437832511007</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.23641710058327</v>
+        <v>17.74821902428575</v>
       </c>
       <c r="AK4" t="n">
-        <v>38.17418283984513</v>
+        <v>38.35257109292667</v>
       </c>
       <c r="AL4" t="n">
-        <v>-113.849790921741</v>
+        <v>-134.8767043913437</v>
       </c>
       <c r="AM4" t="n">
-        <v>-32.5925825215005</v>
+        <v>-34.22345877852664</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.2275757284619757</v>
+        <v>-0.2395084724110762</v>
       </c>
       <c r="AO4" t="n">
-        <v>-18.61286699951254</v>
+        <v>-19.47248922858016</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.145952</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>20.09678</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>92.96769999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>20.42401</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>20.32261</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.0988676</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6.129032</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8.024194</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.16936</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>29.95968</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.609163</v>
       </c>
     </row>
     <row r="5">
@@ -1022,121 +1176,154 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="D5" t="n">
-        <v>1199.86290992</v>
+        <v>1299.7201242</v>
       </c>
       <c r="E5" t="n">
-        <v>320.415589441</v>
+        <v>346.076104124</v>
       </c>
       <c r="F5" t="n">
-        <v>62.2541514527</v>
+        <v>67.6117271863</v>
       </c>
       <c r="G5" t="n">
-        <v>72.98259255885112</v>
+        <v>79.26345508358735</v>
       </c>
       <c r="H5" t="n">
-        <v>394.1059998177961</v>
+        <v>428.0226574513717</v>
       </c>
       <c r="I5" t="n">
-        <v>1.229983848493006</v>
+        <v>1.236787667079175</v>
       </c>
       <c r="J5" t="n">
-        <v>2550.09139118</v>
+        <v>2542.651754</v>
       </c>
       <c r="K5" t="n">
-        <v>24.84139032717415</v>
+        <v>24.76891804962357</v>
       </c>
       <c r="L5" t="n">
-        <v>1394.40211569</v>
+        <v>1501.12002116</v>
       </c>
       <c r="M5" t="n">
-        <v>4.351854783728491</v>
+        <v>4.337543110523877</v>
       </c>
       <c r="N5" t="n">
-        <v>3.201759989156442</v>
+        <v>3.236706916900525</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3326502254066982</v>
+        <v>0.3601964987750724</v>
       </c>
       <c r="P5" t="n">
-        <v>2103.78106115</v>
+        <v>2108.71964232</v>
       </c>
       <c r="Q5" t="n">
-        <v>264.1959399479355</v>
+        <v>263.636130795378</v>
       </c>
       <c r="R5" t="n">
-        <v>85.86759285187357</v>
+        <v>85.550091326344</v>
       </c>
       <c r="S5" t="n">
-        <v>53.55340502049638</v>
+        <v>57.08083544388736</v>
       </c>
       <c r="T5" t="n">
-        <v>44.54043869545165</v>
+        <v>44.29541275227747</v>
       </c>
       <c r="U5" t="n">
-        <v>1199.668</v>
+        <v>1300.024</v>
       </c>
       <c r="V5" t="n">
-        <v>261.7221</v>
+        <v>280.1731</v>
       </c>
       <c r="W5" t="n">
-        <v>99.86499999999999</v>
+        <v>107.281</v>
       </c>
       <c r="X5" t="n">
-        <v>123.442521631644</v>
+        <v>132.6093943139679</v>
       </c>
       <c r="Y5" t="n">
-        <v>259.2292954264524</v>
+        <v>278.4797280593326</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9904753760819295</v>
+        <v>0.9939559795688186</v>
       </c>
       <c r="AA5" t="n">
-        <v>2087.014</v>
+        <v>2062.997</v>
       </c>
       <c r="AB5" t="n">
-        <v>20.33038093128387</v>
+        <v>20.0964223862877</v>
       </c>
       <c r="AC5" t="n">
-        <v>802.8339999999999</v>
+        <v>859.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.067505571749577</v>
+        <v>3.066104490402541</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15411729161031</v>
+        <v>2.180324876051744</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2062992930795192</v>
+        <v>0.2229211108269001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1003.726</v>
+        <v>1003.352</v>
       </c>
       <c r="AH5" t="n">
-        <v>153.3635080573405</v>
+        <v>151.3299523887224</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.03437832511007</v>
+        <v>76.02702393717755</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17.74821902428575</v>
+        <v>19.44642153696666</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.35257109292667</v>
+        <v>38.21826927733208</v>
       </c>
       <c r="AL5" t="n">
-        <v>-134.8767043913437</v>
+        <v>-149.5429293920391</v>
       </c>
       <c r="AM5" t="n">
-        <v>-34.22345877852664</v>
+        <v>-34.9380872224104</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.2395084724110762</v>
+        <v>-0.2428316875103567</v>
       </c>
       <c r="AO5" t="n">
-        <v>-19.47248922858016</v>
+        <v>-19.63406443757911</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.262931</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18.6875</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>96.8399</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>20.45407</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>20.49763</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.0463336</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.804688</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>29.39063</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.074259</v>
       </c>
     </row>
     <row r="6">
@@ -1151,121 +1338,154 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="D6" t="n">
-        <v>1299.7201242</v>
+        <v>1399.82352181</v>
       </c>
       <c r="E6" t="n">
-        <v>346.076104124</v>
+        <v>367.407812665</v>
       </c>
       <c r="F6" t="n">
-        <v>67.6117271863</v>
+        <v>72.3903326484</v>
       </c>
       <c r="G6" t="n">
-        <v>79.26345508358735</v>
+        <v>84.8655716862837</v>
       </c>
       <c r="H6" t="n">
-        <v>428.0226574513717</v>
+        <v>458.274087105932</v>
       </c>
       <c r="I6" t="n">
-        <v>1.236787667079175</v>
+        <v>1.247317208041472</v>
       </c>
       <c r="J6" t="n">
-        <v>2542.651754</v>
+        <v>2506.42407501</v>
       </c>
       <c r="K6" t="n">
-        <v>24.76891804962357</v>
+        <v>24.41601073126204</v>
       </c>
       <c r="L6" t="n">
-        <v>1501.12002116</v>
+        <v>1591.65581007</v>
       </c>
       <c r="M6" t="n">
-        <v>4.337543110523877</v>
+        <v>4.332122930443129</v>
       </c>
       <c r="N6" t="n">
-        <v>3.236706916900525</v>
+        <v>3.241943089107858</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3601964987750724</v>
+        <v>0.3841165943639843</v>
       </c>
       <c r="P6" t="n">
-        <v>2108.71964232</v>
+        <v>2087.90902829</v>
       </c>
       <c r="Q6" t="n">
-        <v>263.636130795378</v>
+        <v>261.1287621659193</v>
       </c>
       <c r="R6" t="n">
-        <v>85.550091326344</v>
+        <v>85.30512622614667</v>
       </c>
       <c r="S6" t="n">
-        <v>57.08083544388736</v>
+        <v>59.57143091889137</v>
       </c>
       <c r="T6" t="n">
-        <v>44.29541275227747</v>
+        <v>43.92148191895775</v>
       </c>
       <c r="U6" t="n">
-        <v>1300.024</v>
+        <v>1400.075</v>
       </c>
       <c r="V6" t="n">
-        <v>280.1731</v>
+        <v>300.4143</v>
       </c>
       <c r="W6" t="n">
-        <v>107.281</v>
+        <v>115.281</v>
       </c>
       <c r="X6" t="n">
-        <v>132.6093943139679</v>
+        <v>142.4981458590853</v>
       </c>
       <c r="Y6" t="n">
-        <v>278.4797280593326</v>
+        <v>299.2461063040791</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9939559795688186</v>
+        <v>0.9961113911823742</v>
       </c>
       <c r="AA6" t="n">
-        <v>2062.997</v>
+        <v>2052.946</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.0964223862877</v>
+        <v>19.99851185059396</v>
       </c>
       <c r="AC6" t="n">
-        <v>859.04</v>
+        <v>924.624</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.066104490402541</v>
+        <v>3.07782951743642</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.180324876051744</v>
+        <v>2.241967495027866</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2229211108269001</v>
+        <v>0.2429402815528524</v>
       </c>
       <c r="AG6" t="n">
-        <v>1003.352</v>
+        <v>1029.969</v>
       </c>
       <c r="AH6" t="n">
-        <v>151.3299523887224</v>
+        <v>151.4528223795006</v>
       </c>
       <c r="AI6" t="n">
-        <v>76.02702393717755</v>
+        <v>75.09742393077627</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19.44642153696666</v>
+        <v>21.8214326817</v>
       </c>
       <c r="AK6" t="n">
-        <v>38.21826927733208</v>
+        <v>38.1355715969526</v>
       </c>
       <c r="AL6" t="n">
-        <v>-149.5429293920391</v>
+        <v>-159.0279808018529</v>
       </c>
       <c r="AM6" t="n">
-        <v>-34.9380872224104</v>
+        <v>-34.70149966500132</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.2428316875103567</v>
+        <v>-0.251205816859098</v>
       </c>
       <c r="AO6" t="n">
-        <v>-19.63406443757911</v>
+        <v>-20.13968982706007</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.450189</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18.96875</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>97.709</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>20.76187</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20.97651</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.2170967</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.320313</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.242188</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>15.10938</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>30.17188</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.316472</v>
       </c>
     </row>
     <row r="7">
@@ -1280,121 +1500,154 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D7" t="n">
-        <v>1399.82352181</v>
+        <v>1499.6824457</v>
       </c>
       <c r="E7" t="n">
-        <v>367.407812665</v>
+        <v>388.694464627</v>
       </c>
       <c r="F7" t="n">
-        <v>72.3903326484</v>
+        <v>77.63584094479999</v>
       </c>
       <c r="G7" t="n">
-        <v>84.8655716862837</v>
+        <v>91.01505386260257</v>
       </c>
       <c r="H7" t="n">
-        <v>458.274087105932</v>
+        <v>491.4812908580539</v>
       </c>
       <c r="I7" t="n">
-        <v>1.247317208041472</v>
+        <v>1.264441188607331</v>
       </c>
       <c r="J7" t="n">
-        <v>2506.42407501</v>
+        <v>2475.06577227</v>
       </c>
       <c r="K7" t="n">
-        <v>24.41601073126204</v>
+        <v>24.11053782113172</v>
       </c>
       <c r="L7" t="n">
-        <v>1591.65581007</v>
+        <v>1689.92398591</v>
       </c>
       <c r="M7" t="n">
-        <v>4.332122930443129</v>
+        <v>4.347692441495634</v>
       </c>
       <c r="N7" t="n">
-        <v>3.241943089107858</v>
+        <v>3.278674470393804</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3841165943639843</v>
+        <v>0.4104028682278533</v>
       </c>
       <c r="P7" t="n">
-        <v>2087.90902829</v>
+        <v>2090.40048932</v>
       </c>
       <c r="Q7" t="n">
-        <v>261.1287621659193</v>
+        <v>260.6430087969362</v>
       </c>
       <c r="R7" t="n">
-        <v>85.30512622614667</v>
+        <v>85.07808412737261</v>
       </c>
       <c r="S7" t="n">
-        <v>59.57143091889137</v>
+        <v>63.15925558260871</v>
       </c>
       <c r="T7" t="n">
-        <v>43.92148191895775</v>
+        <v>43.32666532362657</v>
       </c>
       <c r="U7" t="n">
-        <v>1400.075</v>
+        <v>1500.016</v>
       </c>
       <c r="V7" t="n">
-        <v>300.4143</v>
+        <v>301.1655</v>
       </c>
       <c r="W7" t="n">
-        <v>115.281</v>
+        <v>116.68</v>
       </c>
       <c r="X7" t="n">
-        <v>142.4981458590853</v>
+        <v>144.2274412855377</v>
       </c>
       <c r="Y7" t="n">
-        <v>299.2461063040791</v>
+        <v>302.8776266996292</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9961113911823742</v>
+        <v>1.00568500276303</v>
       </c>
       <c r="AA7" t="n">
-        <v>2052.946</v>
+        <v>1920.083</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.99851185059396</v>
+        <v>18.70424386692295</v>
       </c>
       <c r="AC7" t="n">
-        <v>924.624</v>
+        <v>933.568</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.07782951743642</v>
+        <v>3.099850414473105</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.241967495027866</v>
+        <v>2.15791880391235</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2429402815528524</v>
+        <v>0.2457504738434706</v>
       </c>
       <c r="AG7" t="n">
-        <v>1029.969</v>
+        <v>945.126</v>
       </c>
       <c r="AH7" t="n">
-        <v>151.4528223795006</v>
+        <v>142.6978264604757</v>
       </c>
       <c r="AI7" t="n">
-        <v>75.09742393077627</v>
+        <v>73.8220616060774</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21.8214326817</v>
+        <v>20.80657339648533</v>
       </c>
       <c r="AK7" t="n">
-        <v>38.1355715969526</v>
+        <v>37.77254028111073</v>
       </c>
       <c r="AL7" t="n">
-        <v>-159.0279808018529</v>
+        <v>-188.6036641584247</v>
       </c>
       <c r="AM7" t="n">
-        <v>-34.70149966500132</v>
+        <v>-38.37453585041873</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.251205816859098</v>
+        <v>-0.2587561858443008</v>
       </c>
       <c r="AO7" t="n">
-        <v>-20.13968982706007</v>
+        <v>-20.46407442083548</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.432865</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>18.53125</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>91.85599999999999</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19.21617</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>19.54951</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.3357958</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.773438</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.79688</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>30.375</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.757776</v>
       </c>
     </row>
     <row r="8">
@@ -1409,121 +1662,154 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>1499.6824457</v>
+        <v>1599.77762091</v>
       </c>
       <c r="E8" t="n">
-        <v>388.694464627</v>
+        <v>394.333284808</v>
       </c>
       <c r="F8" t="n">
-        <v>77.63584094479999</v>
+        <v>79.76341055490001</v>
       </c>
       <c r="G8" t="n">
-        <v>91.01505386260257</v>
+        <v>93.50927380410317</v>
       </c>
       <c r="H8" t="n">
-        <v>491.4812908580539</v>
+        <v>504.9500785421571</v>
       </c>
       <c r="I8" t="n">
-        <v>1.264441188607331</v>
+        <v>1.280515994961004</v>
       </c>
       <c r="J8" t="n">
-        <v>2475.06577227</v>
+        <v>2353.82949239</v>
       </c>
       <c r="K8" t="n">
-        <v>24.11053782113172</v>
+        <v>22.92953004990827</v>
       </c>
       <c r="L8" t="n">
-        <v>1689.92398591</v>
+        <v>1757.33848801</v>
       </c>
       <c r="M8" t="n">
-        <v>4.347692441495634</v>
+        <v>4.456480230588814</v>
       </c>
       <c r="N8" t="n">
-        <v>3.278674470393804</v>
+        <v>3.209033350920502</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4104028682278533</v>
+        <v>0.4285883475937811</v>
       </c>
       <c r="P8" t="n">
-        <v>2090.40048932</v>
+        <v>2003.24394734</v>
       </c>
       <c r="Q8" t="n">
-        <v>260.6430087969362</v>
+        <v>254.307230603555</v>
       </c>
       <c r="R8" t="n">
-        <v>85.07808412737261</v>
+        <v>85.40861717388215</v>
       </c>
       <c r="S8" t="n">
-        <v>63.15925558260871</v>
+        <v>65.04774618537127</v>
       </c>
       <c r="T8" t="n">
-        <v>43.32666532362657</v>
+        <v>42.7827691460166</v>
       </c>
       <c r="U8" t="n">
-        <v>1500.016</v>
+        <v>1600.038</v>
       </c>
       <c r="V8" t="n">
-        <v>301.1655</v>
+        <v>300.3554</v>
       </c>
       <c r="W8" t="n">
-        <v>116.68</v>
+        <v>117.308</v>
       </c>
       <c r="X8" t="n">
-        <v>144.2274412855377</v>
+        <v>145.0037082818294</v>
       </c>
       <c r="Y8" t="n">
-        <v>302.8776266996292</v>
+        <v>304.5077873918418</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.00568500276303</v>
+        <v>1.013824913392074</v>
       </c>
       <c r="AA8" t="n">
-        <v>1920.083</v>
+        <v>1795.378</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.70424386692295</v>
+        <v>17.48944600067205</v>
       </c>
       <c r="AC8" t="n">
-        <v>933.568</v>
+        <v>939.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.099850414473105</v>
+        <v>3.12849377770468</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15791880391235</v>
+        <v>2.08444373829525</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2457504738434706</v>
+        <v>0.2476852341967574</v>
       </c>
       <c r="AG8" t="n">
-        <v>945.126</v>
+        <v>871.4739999999999</v>
       </c>
       <c r="AH8" t="n">
-        <v>142.6978264604757</v>
+        <v>134.7685023601441</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.8220616060774</v>
+        <v>72.44488005184792</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20.80657339648533</v>
+        <v>19.76882940174999</v>
       </c>
       <c r="AK8" t="n">
-        <v>37.77254028111073</v>
+        <v>37.46926789348365</v>
       </c>
       <c r="AL8" t="n">
-        <v>-188.6036641584247</v>
+        <v>-200.4422911503153</v>
       </c>
       <c r="AM8" t="n">
-        <v>-38.37453585041873</v>
+        <v>-39.69546687249021</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.2587561858443008</v>
+        <v>-0.2666910815689301</v>
       </c>
       <c r="AO8" t="n">
-        <v>-20.46407442083548</v>
+        <v>-20.8268450076683</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.472774</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17.96875</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>89.8152</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>18.2615</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>18.6857</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.4264984</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.273438</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.148438</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>14.07813</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>30.375</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.795466</v>
       </c>
     </row>
     <row r="9">
@@ -1538,121 +1824,154 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="D9" t="n">
-        <v>1599.77762091</v>
+        <v>1699.63841723</v>
       </c>
       <c r="E9" t="n">
-        <v>394.333284808</v>
+        <v>392.44891672</v>
       </c>
       <c r="F9" t="n">
-        <v>79.76341055490001</v>
+        <v>79.86487850029999</v>
       </c>
       <c r="G9" t="n">
-        <v>93.50927380410317</v>
+        <v>93.62822801910902</v>
       </c>
       <c r="H9" t="n">
-        <v>504.9500785421571</v>
+        <v>505.5924313031887</v>
       </c>
       <c r="I9" t="n">
-        <v>1.280515994961004</v>
+        <v>1.288301253393223</v>
       </c>
       <c r="J9" t="n">
-        <v>2353.82949239</v>
+        <v>2204.98225505</v>
       </c>
       <c r="K9" t="n">
-        <v>22.92953004990827</v>
+        <v>21.47955365507267</v>
       </c>
       <c r="L9" t="n">
-        <v>1757.33848801</v>
+        <v>1781.48985339</v>
       </c>
       <c r="M9" t="n">
-        <v>4.456480230588814</v>
+        <v>4.53941845037895</v>
       </c>
       <c r="N9" t="n">
-        <v>3.209033350920502</v>
+        <v>3.083141085728647</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4285883475937811</v>
+        <v>0.4353538353188192</v>
       </c>
       <c r="P9" t="n">
-        <v>2003.24394734</v>
+        <v>1872.93741169</v>
       </c>
       <c r="Q9" t="n">
-        <v>254.307230603555</v>
+        <v>241.8846982364728</v>
       </c>
       <c r="R9" t="n">
-        <v>85.40861717388215</v>
+        <v>84.90454377874335</v>
       </c>
       <c r="S9" t="n">
-        <v>65.04774618537127</v>
+        <v>64.1654884816061</v>
       </c>
       <c r="T9" t="n">
-        <v>42.7827691460166</v>
+        <v>42.52423108019509</v>
       </c>
       <c r="U9" t="n">
-        <v>1600.038</v>
+        <v>1699.999</v>
       </c>
       <c r="V9" t="n">
-        <v>300.3554</v>
+        <v>296.0968</v>
       </c>
       <c r="W9" t="n">
-        <v>117.308</v>
+        <v>117.119</v>
       </c>
       <c r="X9" t="n">
-        <v>145.0037082818294</v>
+        <v>144.770086526576</v>
       </c>
       <c r="Y9" t="n">
-        <v>304.5077873918418</v>
+        <v>304.0171817058097</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.013824913392074</v>
+        <v>1.026749298559828</v>
       </c>
       <c r="AA9" t="n">
-        <v>1795.378</v>
+        <v>1665.875</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.48944600067205</v>
+        <v>16.22790902883379</v>
       </c>
       <c r="AC9" t="n">
-        <v>939.66</v>
+        <v>935.774</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.12849377770468</v>
+        <v>3.16036512383788</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.08444373829525</v>
+        <v>1.998451808424485</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2476852341967574</v>
+        <v>0.2463620050651257</v>
       </c>
       <c r="AG9" t="n">
-        <v>871.4739999999999</v>
+        <v>791.2596</v>
       </c>
       <c r="AH9" t="n">
-        <v>134.7685023601441</v>
+        <v>126.3173259000818</v>
       </c>
       <c r="AI9" t="n">
-        <v>72.44488005184792</v>
+        <v>70.92075394072056</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19.76882940174999</v>
+        <v>18.32208567917583</v>
       </c>
       <c r="AK9" t="n">
-        <v>37.46926789348365</v>
+        <v>36.99761697452185</v>
       </c>
       <c r="AL9" t="n">
-        <v>-200.4422911503153</v>
+        <v>-201.5752495973791</v>
       </c>
       <c r="AM9" t="n">
-        <v>-39.69546687249021</v>
+        <v>-39.86911929789162</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.2666910815689301</v>
+        <v>-0.2615519548333953</v>
       </c>
       <c r="AO9" t="n">
-        <v>-20.8268450076683</v>
+        <v>-20.30208028941215</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.480467</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>17.34375</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>86.8122</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>17.17241</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>17.70091</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.5316085</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.507813</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.320313</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13.24219</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>29.46094</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.564339</v>
       </c>
     </row>
     <row r="10">
@@ -1667,250 +1986,154 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="D10" t="n">
-        <v>1699.63841723</v>
+        <v>1799.73595333</v>
       </c>
       <c r="E10" t="n">
-        <v>392.44891672</v>
+        <v>394.618160262</v>
       </c>
       <c r="F10" t="n">
-        <v>79.86487850029999</v>
+        <v>81.3583114385</v>
       </c>
       <c r="G10" t="n">
-        <v>93.62822801910902</v>
+        <v>95.37902865005861</v>
       </c>
       <c r="H10" t="n">
-        <v>505.5924313031887</v>
+        <v>515.0467547103166</v>
       </c>
       <c r="I10" t="n">
-        <v>1.288301253393223</v>
+        <v>1.305177527482162</v>
       </c>
       <c r="J10" t="n">
-        <v>2204.98225505</v>
+        <v>2093.79388149</v>
       </c>
       <c r="K10" t="n">
-        <v>21.47955365507267</v>
+        <v>20.39642628285346</v>
       </c>
       <c r="L10" t="n">
-        <v>1781.48985339</v>
+        <v>1839.49337931</v>
       </c>
       <c r="M10" t="n">
-        <v>4.53941845037895</v>
+        <v>4.661451409354044</v>
       </c>
       <c r="N10" t="n">
-        <v>3.083141085728647</v>
+        <v>3.052200566203288</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4353538353188192</v>
+        <v>0.4512066176176181</v>
       </c>
       <c r="P10" t="n">
-        <v>1872.93741169</v>
+        <v>1824.85529229</v>
       </c>
       <c r="Q10" t="n">
-        <v>241.8846982364728</v>
+        <v>236.7196328849409</v>
       </c>
       <c r="R10" t="n">
-        <v>84.90454377874335</v>
+        <v>84.49937132592183</v>
       </c>
       <c r="S10" t="n">
-        <v>64.1654884816061</v>
+        <v>66.41701487097963</v>
       </c>
       <c r="T10" t="n">
-        <v>42.52423108019509</v>
+        <v>41.97438206424157</v>
       </c>
       <c r="U10" t="n">
-        <v>1699.999</v>
+        <v>1799.979</v>
       </c>
       <c r="V10" t="n">
-        <v>296.0968</v>
+        <v>291.8231</v>
       </c>
       <c r="W10" t="n">
-        <v>117.119</v>
+        <v>116.542</v>
       </c>
       <c r="X10" t="n">
-        <v>144.770086526576</v>
+        <v>144.0568603213844</v>
       </c>
       <c r="Y10" t="n">
-        <v>304.0171817058097</v>
+        <v>302.5194066749073</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.026749298559828</v>
+        <v>1.036653392671476</v>
       </c>
       <c r="AA10" t="n">
-        <v>1665.875</v>
+        <v>1551.491</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.22790902883379</v>
+        <v>15.11365186887033</v>
       </c>
       <c r="AC10" t="n">
-        <v>935.774</v>
+        <v>931.751</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.16036512383788</v>
+        <v>3.192862388207102</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.998451808424485</v>
+        <v>1.925254237226219</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2463620050651257</v>
+        <v>0.2448460278463756</v>
       </c>
       <c r="AG10" t="n">
-        <v>791.2596</v>
+        <v>722.6549</v>
       </c>
       <c r="AH10" t="n">
-        <v>126.3173259000818</v>
+        <v>118.9052406400124</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.92075394072056</v>
+        <v>69.39801729498907</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.32208567917583</v>
+        <v>16.99069460301212</v>
       </c>
       <c r="AK10" t="n">
-        <v>36.99761697452185</v>
+        <v>36.64414503972399</v>
       </c>
       <c r="AL10" t="n">
-        <v>-201.5752495973791</v>
+        <v>-212.5273480354093</v>
       </c>
       <c r="AM10" t="n">
-        <v>-39.86911929789162</v>
+        <v>-41.26370006057864</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.2615519548333953</v>
+        <v>-0.2685241348106859</v>
       </c>
       <c r="AO10" t="n">
-        <v>-20.30208028941215</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sway_p8_c13_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SWay_P8_C13_Full Load Curve_Brazil_397kW_D85B15 vs P251191_C13_Etanol_Full_Load_Curve_Rev_26</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1799.73595333</v>
-      </c>
-      <c r="E11" t="n">
-        <v>394.618160262</v>
-      </c>
-      <c r="F11" t="n">
-        <v>81.3583114385</v>
-      </c>
-      <c r="G11" t="n">
-        <v>95.37902865005861</v>
-      </c>
-      <c r="H11" t="n">
-        <v>515.0467547103166</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.305177527482162</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2093.79388149</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20.39642628285346</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1839.49337931</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.661451409354044</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.052200566203288</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.4512066176176181</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1824.85529229</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>236.7196328849409</v>
-      </c>
-      <c r="R11" t="n">
-        <v>84.49937132592183</v>
-      </c>
-      <c r="S11" t="n">
-        <v>66.41701487097963</v>
-      </c>
-      <c r="T11" t="n">
-        <v>41.97438206424157</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1799.979</v>
-      </c>
-      <c r="V11" t="n">
-        <v>291.8231</v>
-      </c>
-      <c r="W11" t="n">
-        <v>116.542</v>
-      </c>
-      <c r="X11" t="n">
-        <v>144.0568603213844</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>302.5194066749073</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.036653392671476</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1551.491</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>15.11365186887033</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>931.751</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.192862388207102</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.925254237226219</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.2448460278463756</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>722.6549</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>118.9052406400124</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>69.39801729498907</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>16.99069460301212</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>36.64414503972399</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-212.5273480354093</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-41.26370006057864</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-0.2685241348106859</v>
-      </c>
-      <c r="AO11" t="n">
         <v>-20.57376327408119</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.527098</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17.15625</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>81.47969000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15.94563</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>16.56811</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.6255855</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.289063</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13.22656</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.309934</v>
       </c>
     </row>
   </sheetData>
